--- a/output/pdf_financials_xlsx/RKL.xlsx
+++ b/output/pdf_financials_xlsx/RKL.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.091698</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.105698</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.414698</v>
       </c>
     </row>
     <row r="93">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>2.89098</v>
+        <v>1.559467</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.78976</v>
+        <v>0.687374</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.290329</v>
+        <v>1.032621</v>
       </c>
     </row>
     <row r="119">
@@ -3146,7 +3146,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>1.091698</v>
       </c>
@@ -3692,7 +3696,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-1.331513</v>
       </c>

--- a/output/pdf_financials_xlsx/RKL.xlsx
+++ b/output/pdf_financials_xlsx/RKL.xlsx
@@ -979,10 +979,10 @@
         <v>0.122489</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.058397</v>
+        <v>0.005273</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.023124</v>
       </c>
     </row>
     <row r="35">
@@ -1011,10 +1011,10 @@
         <v>0.874781</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.159246</v>
+        <v>0.106122</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.023124</v>
       </c>
     </row>
     <row r="37">
@@ -1203,10 +1203,10 @@
         <v>0.130387</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>6.9e-05</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.065979</v>
+        <v>0.042855</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/RKL.xlsx
+++ b/output/pdf_financials_xlsx/RKL.xlsx
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.157723</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.038439</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.039583</v>
       </c>
     </row>
     <row r="116">
@@ -3760,7 +3760,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.157723</v>
       </c>
